--- a/geoprob_pipe/pre_processing/parameter_input/input_voorstel_v3.xlsx
+++ b/geoprob_pipe/pre_processing/parameter_input/input_voorstel_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CP\git_clones\GeoProb-Pipe\GeoProb-PipeV2\GeoProb-Pipe\geoprob_pipe\pre_processing\parameter_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8CC692-EC25-4945-8072-9F0A91FACFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EBC111-6BB2-44E6-892B-49885581034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4072986C-855A-4E04-BDA4-92C994E74780}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4072986C-855A-4E04-BDA4-92C994E74780}"/>
   </bookViews>
   <sheets>
     <sheet name="Model parameters" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="147">
   <si>
     <t>parameter</t>
   </si>
@@ -976,17 +976,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAEDF215-1BC2-44F5-8521-4305F21BD459}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="52.7109375" style="14" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="14"/>
+    <col min="1" max="1" width="23.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.5546875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="52.6640625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
@@ -1003,14 +1003,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>9</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>0</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>26</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>25</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>20</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>58</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>59</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>64</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>55</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>31</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>65</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>60</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>27</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>61</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>62</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>70</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>71</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>50</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>51</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>66</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>67</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>52</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>68</v>
       </c>
@@ -1383,15 +1383,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9313D639-575E-4463-A991-9636CAC84E2D}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
     <col min="2" max="2" width="20" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="2"/>
+    <col min="4" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1424,9 +1424,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -1435,9 +1435,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
@@ -1446,9 +1446,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -1457,9 +1457,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -1468,9 +1468,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -1479,9 +1479,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>13</v>
@@ -1490,9 +1490,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1501,9 +1501,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>13</v>
@@ -1512,9 +1512,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1523,9 +1523,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -1534,9 +1534,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1545,9 +1545,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>13</v>
@@ -1556,71 +1556,23 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>7</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>7</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>8</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>8</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>9</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.5</v>
-      </c>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="7"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{9313D639-575E-4463-A991-9636CAC84E2D}"/>
@@ -1631,21 +1583,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90D4119-5ABA-4602-81BD-BF6C31F178E4}">
   <dimension ref="A1:J336"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.85546875" style="11" customWidth="1"/>
+    <col min="1" max="2" width="22.88671875" style="11" customWidth="1"/>
     <col min="3" max="3" width="13" style="11" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="11" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="38.85546875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="38.88671875" style="11" customWidth="1"/>
     <col min="10" max="10" width="66" style="11" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="11"/>
+    <col min="11" max="16384" width="8.88671875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
@@ -1675,7 +1627,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="126.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="126.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>120</v>
       </c>
@@ -1705,7 +1657,7 @@
       </c>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -1737,7 +1689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -1769,7 +1721,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
@@ -1786,7 +1738,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1803,7 +1755,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1811,7 +1763,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>27</v>
       </c>
@@ -1825,7 +1777,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
@@ -1842,7 +1794,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
@@ -1859,7 +1811,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
@@ -1876,7 +1828,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
@@ -1893,7 +1845,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>31</v>
       </c>
@@ -1910,7 +1862,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>31</v>
       </c>
@@ -1927,7 +1879,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>31</v>
       </c>
@@ -1944,7 +1896,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
@@ -1961,7 +1913,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>31</v>
       </c>
@@ -1978,7 +1930,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>31</v>
       </c>
@@ -1995,7 +1947,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>31</v>
       </c>
@@ -2012,7 +1964,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>31</v>
       </c>
@@ -2029,7 +1981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -2046,7 +1998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
@@ -2063,7 +2015,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>31</v>
       </c>
@@ -2080,7 +2032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
@@ -2097,7 +2049,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -2114,7 +2066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>31</v>
       </c>
@@ -2131,7 +2083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>31</v>
       </c>
@@ -2148,7 +2100,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>31</v>
       </c>
@@ -2165,7 +2117,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>31</v>
       </c>
@@ -2182,7 +2134,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>31</v>
       </c>
@@ -2199,7 +2151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>31</v>
       </c>
@@ -2216,7 +2168,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>31</v>
       </c>
@@ -2233,7 +2185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>31</v>
       </c>
@@ -2250,7 +2202,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>31</v>
       </c>
@@ -2267,7 +2219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>31</v>
       </c>
@@ -2284,7 +2236,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>31</v>
       </c>
@@ -2301,7 +2253,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>31</v>
       </c>
@@ -2318,7 +2270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>31</v>
       </c>
@@ -2335,7 +2287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>31</v>
       </c>
@@ -2352,7 +2304,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>31</v>
       </c>
@@ -2369,7 +2321,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>31</v>
       </c>
@@ -2386,7 +2338,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>31</v>
       </c>
@@ -2403,7 +2355,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>31</v>
       </c>
@@ -2420,7 +2372,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>31</v>
       </c>
@@ -2437,7 +2389,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>31</v>
       </c>
@@ -2454,7 +2406,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>31</v>
       </c>
@@ -2471,7 +2423,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>31</v>
       </c>
@@ -2488,7 +2440,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>31</v>
       </c>
@@ -2505,7 +2457,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>31</v>
       </c>
@@ -2522,7 +2474,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>31</v>
       </c>
@@ -2539,7 +2491,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>31</v>
       </c>
@@ -2556,7 +2508,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>31</v>
       </c>
@@ -2573,7 +2525,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
         <v>31</v>
       </c>
@@ -2590,7 +2542,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
         <v>31</v>
       </c>
@@ -2607,7 +2559,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>31</v>
       </c>
@@ -2624,7 +2576,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>31</v>
       </c>
@@ -2641,7 +2593,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>31</v>
       </c>
@@ -2658,7 +2610,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>31</v>
       </c>
@@ -2675,7 +2627,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
         <v>31</v>
       </c>
@@ -2692,7 +2644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
         <v>31</v>
       </c>
@@ -2709,7 +2661,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
         <v>31</v>
       </c>
@@ -2726,7 +2678,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
         <v>31</v>
       </c>
@@ -2743,7 +2695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
         <v>31</v>
       </c>
@@ -2760,7 +2712,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
         <v>31</v>
       </c>
@@ -2777,7 +2729,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
         <v>31</v>
       </c>
@@ -2794,7 +2746,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
         <v>31</v>
       </c>
@@ -2811,7 +2763,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
         <v>31</v>
       </c>
@@ -2828,7 +2780,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
         <v>31</v>
       </c>
@@ -2845,7 +2797,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
         <v>31</v>
       </c>
@@ -2862,7 +2814,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
         <v>31</v>
       </c>
@@ -2879,7 +2831,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
         <v>31</v>
       </c>
@@ -2896,7 +2848,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
         <v>31</v>
       </c>
@@ -2913,7 +2865,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>31</v>
       </c>
@@ -2930,7 +2882,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
         <v>31</v>
       </c>
@@ -2947,7 +2899,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
         <v>31</v>
       </c>
@@ -2964,7 +2916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
         <v>31</v>
       </c>
@@ -2981,7 +2933,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
         <v>31</v>
       </c>
@@ -2998,7 +2950,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
         <v>31</v>
       </c>
@@ -3015,7 +2967,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>31</v>
       </c>
@@ -3032,7 +2984,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>31</v>
       </c>
@@ -3049,7 +3001,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
         <v>31</v>
       </c>
@@ -3066,7 +3018,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
         <v>31</v>
       </c>
@@ -3083,7 +3035,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
         <v>31</v>
       </c>
@@ -3100,7 +3052,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
         <v>31</v>
       </c>
@@ -3117,7 +3069,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
         <v>31</v>
       </c>
@@ -3134,7 +3086,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
         <v>31</v>
       </c>
@@ -3151,7 +3103,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
         <v>31</v>
       </c>
@@ -3168,7 +3120,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
         <v>31</v>
       </c>
@@ -3185,7 +3137,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
         <v>31</v>
       </c>
@@ -3202,7 +3154,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
         <v>31</v>
       </c>
@@ -3219,7 +3171,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
         <v>31</v>
       </c>
@@ -3236,7 +3188,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
         <v>31</v>
       </c>
@@ -3253,7 +3205,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
         <v>31</v>
       </c>
@@ -3270,7 +3222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
         <v>31</v>
       </c>
@@ -3287,7 +3239,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
         <v>31</v>
       </c>
@@ -3304,7 +3256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
         <v>31</v>
       </c>
@@ -3321,7 +3273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
         <v>31</v>
       </c>
@@ -3338,7 +3290,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
         <v>31</v>
       </c>
@@ -3355,7 +3307,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
         <v>31</v>
       </c>
@@ -3372,7 +3324,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
         <v>31</v>
       </c>
@@ -3389,7 +3341,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
         <v>31</v>
       </c>
@@ -3406,7 +3358,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
         <v>31</v>
       </c>
@@ -3423,7 +3375,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
         <v>31</v>
       </c>
@@ -3440,7 +3392,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
         <v>31</v>
       </c>
@@ -3457,7 +3409,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
         <v>31</v>
       </c>
@@ -3474,7 +3426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
         <v>31</v>
       </c>
@@ -3491,7 +3443,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
         <v>31</v>
       </c>
@@ -3508,7 +3460,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
         <v>31</v>
       </c>
@@ -3525,7 +3477,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
         <v>31</v>
       </c>
@@ -3542,7 +3494,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
         <v>31</v>
       </c>
@@ -3559,7 +3511,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
         <v>50</v>
       </c>
@@ -3576,7 +3528,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
         <v>50</v>
       </c>
@@ -3593,7 +3545,7 @@
         <v>11.31</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
         <v>50</v>
       </c>
@@ -3610,7 +3562,7 @@
         <v>14.16</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
         <v>50</v>
       </c>
@@ -3627,7 +3579,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
         <v>50</v>
       </c>
@@ -3644,7 +3596,7 @@
         <v>12.43</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
         <v>50</v>
       </c>
@@ -3661,7 +3613,7 @@
         <v>13.13</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
         <v>50</v>
       </c>
@@ -3678,7 +3630,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
         <v>50</v>
       </c>
@@ -3695,7 +3647,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
         <v>50</v>
       </c>
@@ -3712,7 +3664,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
         <v>50</v>
       </c>
@@ -3729,7 +3681,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
         <v>50</v>
       </c>
@@ -3746,7 +3698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>50</v>
       </c>
@@ -3763,7 +3715,7 @@
         <v>10.34</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
         <v>50</v>
       </c>
@@ -3780,7 +3732,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>50</v>
       </c>
@@ -3797,7 +3749,7 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
         <v>50</v>
       </c>
@@ -3814,7 +3766,7 @@
         <v>9.99</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
         <v>50</v>
       </c>
@@ -3831,7 +3783,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
         <v>50</v>
       </c>
@@ -3848,7 +3800,7 @@
         <v>10.59</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
         <v>50</v>
       </c>
@@ -3865,7 +3817,7 @@
         <v>10.49</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
         <v>50</v>
       </c>
@@ -3882,7 +3834,7 @@
         <v>10.55</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>50</v>
       </c>
@@ -3899,7 +3851,7 @@
         <v>10.28</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="11" t="s">
         <v>50</v>
       </c>
@@ -3916,7 +3868,7 @@
         <v>10.17</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
         <v>50</v>
       </c>
@@ -3933,7 +3885,7 @@
         <v>10.08</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="11" t="s">
         <v>50</v>
       </c>
@@ -3950,7 +3902,7 @@
         <v>9.92</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="11" t="s">
         <v>50</v>
       </c>
@@ -3967,7 +3919,7 @@
         <v>10.31</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
         <v>50</v>
       </c>
@@ -3984,7 +3936,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="11" t="s">
         <v>50</v>
       </c>
@@ -4001,7 +3953,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
         <v>50</v>
       </c>
@@ -4018,7 +3970,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
         <v>50</v>
       </c>
@@ -4035,7 +3987,7 @@
         <v>11.11</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
         <v>50</v>
       </c>
@@ -4052,7 +4004,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
         <v>50</v>
       </c>
@@ -4069,7 +4021,7 @@
         <v>10.97</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
         <v>50</v>
       </c>
@@ -4086,7 +4038,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
         <v>50</v>
       </c>
@@ -4103,7 +4055,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
         <v>50</v>
       </c>
@@ -4120,7 +4072,7 @@
         <v>9.36</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="11" t="s">
         <v>50</v>
       </c>
@@ -4137,7 +4089,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
         <v>50</v>
       </c>
@@ -4154,7 +4106,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="11" t="s">
         <v>50</v>
       </c>
@@ -4171,7 +4123,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
         <v>50</v>
       </c>
@@ -4188,7 +4140,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="11" t="s">
         <v>50</v>
       </c>
@@ -4205,7 +4157,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="11" t="s">
         <v>50</v>
       </c>
@@ -4222,7 +4174,7 @@
         <v>9.24</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
         <v>50</v>
       </c>
@@ -4239,7 +4191,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
         <v>50</v>
       </c>
@@ -4256,7 +4208,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
         <v>50</v>
       </c>
@@ -4273,7 +4225,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="11" t="s">
         <v>50</v>
       </c>
@@ -4290,7 +4242,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
         <v>50</v>
       </c>
@@ -4307,7 +4259,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
         <v>50</v>
       </c>
@@ -4324,7 +4276,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
         <v>50</v>
       </c>
@@ -4341,7 +4293,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
         <v>50</v>
       </c>
@@ -4358,7 +4310,7 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="11" t="s">
         <v>50</v>
       </c>
@@ -4375,7 +4327,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="11" t="s">
         <v>50</v>
       </c>
@@ -4392,7 +4344,7 @@
         <v>10.43</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
         <v>50</v>
       </c>
@@ -4409,7 +4361,7 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="11" t="s">
         <v>50</v>
       </c>
@@ -4426,7 +4378,7 @@
         <v>10.56</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="11" t="s">
         <v>50</v>
       </c>
@@ -4443,7 +4395,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="11" t="s">
         <v>50</v>
       </c>
@@ -4460,7 +4412,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
         <v>50</v>
       </c>
@@ -4477,7 +4429,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="11" t="s">
         <v>50</v>
       </c>
@@ -4494,7 +4446,7 @@
         <v>9.59</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="11" t="s">
         <v>50</v>
       </c>
@@ -4511,7 +4463,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="11" t="s">
         <v>50</v>
       </c>
@@ -4528,7 +4480,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
         <v>50</v>
       </c>
@@ -4545,7 +4497,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
         <v>50</v>
       </c>
@@ -4562,7 +4514,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="11" t="s">
         <v>50</v>
       </c>
@@ -4579,7 +4531,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="11" t="s">
         <v>50</v>
       </c>
@@ -4596,7 +4548,7 @@
         <v>10.45</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="11" t="s">
         <v>50</v>
       </c>
@@ -4613,7 +4565,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="11" t="s">
         <v>50</v>
       </c>
@@ -4630,7 +4582,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="11" t="s">
         <v>50</v>
       </c>
@@ -4647,7 +4599,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="11" t="s">
         <v>50</v>
       </c>
@@ -4664,7 +4616,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="11" t="s">
         <v>50</v>
       </c>
@@ -4681,7 +4633,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="11" t="s">
         <v>50</v>
       </c>
@@ -4698,7 +4650,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>50</v>
       </c>
@@ -4715,7 +4667,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>50</v>
       </c>
@@ -4732,7 +4684,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>50</v>
       </c>
@@ -4749,7 +4701,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>50</v>
       </c>
@@ -4766,7 +4718,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>50</v>
       </c>
@@ -4783,7 +4735,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>50</v>
       </c>
@@ -4800,7 +4752,7 @@
         <v>10.58</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>50</v>
       </c>
@@ -4817,7 +4769,7 @@
         <v>9.93</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="11" t="s">
         <v>50</v>
       </c>
@@ -4834,7 +4786,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="11" t="s">
         <v>50</v>
       </c>
@@ -4851,7 +4803,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="11" t="s">
         <v>50</v>
       </c>
@@ -4868,7 +4820,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="11" t="s">
         <v>50</v>
       </c>
@@ -4885,7 +4837,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="11" t="s">
         <v>50</v>
       </c>
@@ -4902,7 +4854,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="11" t="s">
         <v>50</v>
       </c>
@@ -4919,7 +4871,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="11" t="s">
         <v>50</v>
       </c>
@@ -4936,7 +4888,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="11" t="s">
         <v>50</v>
       </c>
@@ -4953,7 +4905,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="11" t="s">
         <v>50</v>
       </c>
@@ -4970,7 +4922,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="11" t="s">
         <v>50</v>
       </c>
@@ -4987,7 +4939,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="11" t="s">
         <v>50</v>
       </c>
@@ -5004,7 +4956,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="11" t="s">
         <v>50</v>
       </c>
@@ -5021,7 +4973,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="11" t="s">
         <v>50</v>
       </c>
@@ -5038,7 +4990,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="11" t="s">
         <v>50</v>
       </c>
@@ -5055,7 +5007,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="11" t="s">
         <v>50</v>
       </c>
@@ -5072,7 +5024,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="11" t="s">
         <v>50</v>
       </c>
@@ -5089,7 +5041,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="11" t="s">
         <v>50</v>
       </c>
@@ -5106,7 +5058,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="11" t="s">
         <v>50</v>
       </c>
@@ -5123,7 +5075,7 @@
         <v>8.6300000000000008</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="11" t="s">
         <v>50</v>
       </c>
@@ -5140,7 +5092,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="11" t="s">
         <v>50</v>
       </c>
@@ -5157,7 +5109,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="11" t="s">
         <v>50</v>
       </c>
@@ -5174,7 +5126,7 @@
         <v>8.91</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="11" t="s">
         <v>50</v>
       </c>
@@ -5191,7 +5143,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="11" t="s">
         <v>50</v>
       </c>
@@ -5208,7 +5160,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="11" t="s">
         <v>50</v>
       </c>
@@ -5225,7 +5177,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="11" t="s">
         <v>50</v>
       </c>
@@ -5242,7 +5194,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="11" t="s">
         <v>50</v>
       </c>
@@ -5259,7 +5211,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="11" t="s">
         <v>50</v>
       </c>
@@ -5276,7 +5228,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="11" t="s">
         <v>50</v>
       </c>
@@ -5293,7 +5245,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="11" t="s">
         <v>51</v>
       </c>
@@ -5310,7 +5262,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="11" t="s">
         <v>51</v>
       </c>
@@ -5327,7 +5279,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="11" t="s">
         <v>51</v>
       </c>
@@ -5344,7 +5296,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="11" t="s">
         <v>51</v>
       </c>
@@ -5361,7 +5313,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="11" t="s">
         <v>51</v>
       </c>
@@ -5378,7 +5330,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="11" t="s">
         <v>51</v>
       </c>
@@ -5395,7 +5347,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="11" t="s">
         <v>51</v>
       </c>
@@ -5412,7 +5364,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="11" t="s">
         <v>51</v>
       </c>
@@ -5429,7 +5381,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="11" t="s">
         <v>51</v>
       </c>
@@ -5446,7 +5398,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="11" t="s">
         <v>51</v>
       </c>
@@ -5463,7 +5415,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="11" t="s">
         <v>51</v>
       </c>
@@ -5480,7 +5432,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="11" t="s">
         <v>51</v>
       </c>
@@ -5497,7 +5449,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="11" t="s">
         <v>51</v>
       </c>
@@ -5514,7 +5466,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="11" t="s">
         <v>51</v>
       </c>
@@ -5531,7 +5483,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="11" t="s">
         <v>51</v>
       </c>
@@ -5548,7 +5500,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="11" t="s">
         <v>51</v>
       </c>
@@ -5565,7 +5517,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="11" t="s">
         <v>51</v>
       </c>
@@ -5582,7 +5534,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="11" t="s">
         <v>51</v>
       </c>
@@ -5599,7 +5551,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="11" t="s">
         <v>51</v>
       </c>
@@ -5616,7 +5568,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="11" t="s">
         <v>51</v>
       </c>
@@ -5633,7 +5585,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="11" t="s">
         <v>51</v>
       </c>
@@ -5650,7 +5602,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="11" t="s">
         <v>51</v>
       </c>
@@ -5667,7 +5619,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="11" t="s">
         <v>51</v>
       </c>
@@ -5684,7 +5636,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="11" t="s">
         <v>51</v>
       </c>
@@ -5701,7 +5653,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="11" t="s">
         <v>51</v>
       </c>
@@ -5718,7 +5670,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="11" t="s">
         <v>51</v>
       </c>
@@ -5735,7 +5687,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="11" t="s">
         <v>51</v>
       </c>
@@ -5752,7 +5704,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="11" t="s">
         <v>51</v>
       </c>
@@ -5769,7 +5721,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="11" t="s">
         <v>51</v>
       </c>
@@ -5786,7 +5738,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="11" t="s">
         <v>51</v>
       </c>
@@ -5803,7 +5755,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="11" t="s">
         <v>51</v>
       </c>
@@ -5820,7 +5772,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="11" t="s">
         <v>51</v>
       </c>
@@ -5837,7 +5789,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="11" t="s">
         <v>51</v>
       </c>
@@ -5854,7 +5806,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="11" t="s">
         <v>51</v>
       </c>
@@ -5871,7 +5823,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="11" t="s">
         <v>51</v>
       </c>
@@ -5888,7 +5840,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="11" t="s">
         <v>51</v>
       </c>
@@ -5905,7 +5857,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="11" t="s">
         <v>51</v>
       </c>
@@ -5922,7 +5874,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="11" t="s">
         <v>51</v>
       </c>
@@ -5939,7 +5891,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="11" t="s">
         <v>51</v>
       </c>
@@ -5956,7 +5908,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="11" t="s">
         <v>51</v>
       </c>
@@ -5973,7 +5925,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="11" t="s">
         <v>51</v>
       </c>
@@ -5990,7 +5942,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="11" t="s">
         <v>51</v>
       </c>
@@ -6007,7 +5959,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="11" t="s">
         <v>51</v>
       </c>
@@ -6024,7 +5976,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="11" t="s">
         <v>51</v>
       </c>
@@ -6041,7 +5993,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="11" t="s">
         <v>51</v>
       </c>
@@ -6058,7 +6010,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="11" t="s">
         <v>51</v>
       </c>
@@ -6075,7 +6027,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="11" t="s">
         <v>51</v>
       </c>
@@ -6092,7 +6044,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="11" t="s">
         <v>51</v>
       </c>
@@ -6109,7 +6061,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="11" t="s">
         <v>51</v>
       </c>
@@ -6126,7 +6078,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="11" t="s">
         <v>51</v>
       </c>
@@ -6143,7 +6095,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="11" t="s">
         <v>51</v>
       </c>
@@ -6160,7 +6112,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="11" t="s">
         <v>51</v>
       </c>
@@ -6177,7 +6129,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="11" t="s">
         <v>51</v>
       </c>
@@ -6194,7 +6146,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="11" t="s">
         <v>51</v>
       </c>
@@ -6211,7 +6163,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="11" t="s">
         <v>51</v>
       </c>
@@ -6228,7 +6180,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="11" t="s">
         <v>51</v>
       </c>
@@ -6245,7 +6197,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="11" t="s">
         <v>51</v>
       </c>
@@ -6262,7 +6214,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="11" t="s">
         <v>51</v>
       </c>
@@ -6279,7 +6231,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="11" t="s">
         <v>51</v>
       </c>
@@ -6296,7 +6248,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="11" t="s">
         <v>51</v>
       </c>
@@ -6313,7 +6265,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="11" t="s">
         <v>51</v>
       </c>
@@ -6330,7 +6282,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="11" t="s">
         <v>51</v>
       </c>
@@ -6347,7 +6299,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="11" t="s">
         <v>51</v>
       </c>
@@ -6364,7 +6316,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="11" t="s">
         <v>51</v>
       </c>
@@ -6381,7 +6333,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="11" t="s">
         <v>51</v>
       </c>
@@ -6398,7 +6350,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="11" t="s">
         <v>51</v>
       </c>
@@ -6415,7 +6367,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="11" t="s">
         <v>51</v>
       </c>
@@ -6432,7 +6384,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="11" t="s">
         <v>51</v>
       </c>
@@ -6449,7 +6401,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="11" t="s">
         <v>51</v>
       </c>
@@ -6466,7 +6418,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="11" t="s">
         <v>51</v>
       </c>
@@ -6483,7 +6435,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="11" t="s">
         <v>51</v>
       </c>
@@ -6500,7 +6452,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="11" t="s">
         <v>51</v>
       </c>
@@ -6517,7 +6469,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="11" t="s">
         <v>51</v>
       </c>
@@ -6534,7 +6486,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="11" t="s">
         <v>51</v>
       </c>
@@ -6551,7 +6503,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="11" t="s">
         <v>51</v>
       </c>
@@ -6568,7 +6520,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="11" t="s">
         <v>51</v>
       </c>
@@ -6585,7 +6537,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="11" t="s">
         <v>51</v>
       </c>
@@ -6602,7 +6554,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="11" t="s">
         <v>51</v>
       </c>
@@ -6619,7 +6571,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="11" t="s">
         <v>51</v>
       </c>
@@ -6636,7 +6588,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="11" t="s">
         <v>51</v>
       </c>
@@ -6653,7 +6605,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="11" t="s">
         <v>51</v>
       </c>
@@ -6670,7 +6622,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="11" t="s">
         <v>51</v>
       </c>
@@ -6687,7 +6639,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="11" t="s">
         <v>51</v>
       </c>
@@ -6704,7 +6656,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="11" t="s">
         <v>51</v>
       </c>
@@ -6721,7 +6673,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="11" t="s">
         <v>51</v>
       </c>
@@ -6738,7 +6690,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="11" t="s">
         <v>51</v>
       </c>
@@ -6755,7 +6707,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="11" t="s">
         <v>51</v>
       </c>
@@ -6772,7 +6724,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="11" t="s">
         <v>51</v>
       </c>
@@ -6789,7 +6741,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="11" t="s">
         <v>51</v>
       </c>
@@ -6806,7 +6758,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="11" t="s">
         <v>51</v>
       </c>
@@ -6823,7 +6775,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="11" t="s">
         <v>51</v>
       </c>
@@ -6840,7 +6792,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="11" t="s">
         <v>51</v>
       </c>
@@ -6857,7 +6809,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="11" t="s">
         <v>51</v>
       </c>
@@ -6874,7 +6826,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="11" t="s">
         <v>51</v>
       </c>
@@ -6891,7 +6843,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="11" t="s">
         <v>51</v>
       </c>
@@ -6908,7 +6860,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="11" t="s">
         <v>51</v>
       </c>
@@ -6925,7 +6877,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="11" t="s">
         <v>51</v>
       </c>
@@ -6942,7 +6894,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="11" t="s">
         <v>51</v>
       </c>
@@ -6959,7 +6911,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="11" t="s">
         <v>51</v>
       </c>
@@ -6976,7 +6928,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="11" t="s">
         <v>51</v>
       </c>
@@ -6993,7 +6945,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="11" t="s">
         <v>51</v>
       </c>
@@ -7010,7 +6962,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="11" t="s">
         <v>51</v>
       </c>
@@ -7027,7 +6979,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="11" t="s">
         <v>52</v>
       </c>
@@ -7050,7 +7002,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="11" t="s">
         <v>52</v>
       </c>
@@ -7073,7 +7025,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="11" t="s">
         <v>52</v>
       </c>
@@ -7096,7 +7048,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="11" t="s">
         <v>52</v>
       </c>
@@ -7119,7 +7071,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="11" t="s">
         <v>52</v>
       </c>
@@ -7142,7 +7094,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="11" t="s">
         <v>52</v>
       </c>
@@ -7165,7 +7117,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="11" t="s">
         <v>52</v>
       </c>
@@ -7188,7 +7140,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="11" t="s">
         <v>52</v>
       </c>
@@ -7211,7 +7163,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="11" t="s">
         <v>52</v>
       </c>
@@ -7234,7 +7186,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="11" t="s">
         <v>52</v>
       </c>
@@ -7257,7 +7209,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="11" t="s">
         <v>52</v>
       </c>
@@ -7280,7 +7232,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="11" t="s">
         <v>52</v>
       </c>
@@ -7303,7 +7255,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="11" t="s">
         <v>52</v>
       </c>
@@ -7326,7 +7278,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="11" t="s">
         <v>52</v>
       </c>
@@ -7349,7 +7301,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="11" t="s">
         <v>52</v>
       </c>
@@ -7372,7 +7324,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="11" t="s">
         <v>52</v>
       </c>
@@ -7395,7 +7347,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="11" t="s">
         <v>52</v>
       </c>
@@ -7418,7 +7370,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="11" t="s">
         <v>52</v>
       </c>
@@ -7441,7 +7393,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="11" t="s">
         <v>55</v>
       </c>
@@ -7464,7 +7416,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="11" t="s">
         <v>55</v>
       </c>
@@ -7487,7 +7439,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="11" t="s">
         <v>55</v>
       </c>
@@ -7510,7 +7462,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="11" t="s">
         <v>55</v>
       </c>
@@ -7536,18 +7488,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE6525A-680B-4461-9F3B-3E1CE43163B1}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
-    <col min="2" max="2" width="72.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="2"/>
-    <col min="5" max="6" width="10.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="72.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="2"/>
+    <col min="5" max="6" width="10.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="35" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="2"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>125</v>
       </c>
@@ -7570,7 +7522,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>129</v>
       </c>
@@ -7585,7 +7537,7 @@
       </c>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:7" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>128</v>
       </c>
@@ -7608,7 +7560,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>142</v>
       </c>
@@ -7628,55 +7580,55 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C8" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C10" s="7"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C11" s="7"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C12" s="7"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C13" s="7"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C14" s="7"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C15" s="7"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C16" s="7"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" s="7"/>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" s="7"/>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C19" s="7"/>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C21" s="7"/>
     </row>
   </sheetData>
